--- a/daily_matches/job_matches_2026-09-26.xlsx
+++ b/daily_matches/job_matches_2026-09-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect</t>
+          <t>Senior Python Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, ChromaDB</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,347 +496,347 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536f7d54c3314639</t>
+          <t>https://www.indeed.com/viewjob?jk=dac7d146ce85fb43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b32e022f59434ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Agentic Data Engineer, IC2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a560148a8830091</t>
+          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Senior Engineer, Customer Store Experience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e2607363a78874</t>
+          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Kubernetes, Git, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, EC2, Kubernetes, Git, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
+          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, BigQuery, BigQuery, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d5be4c5136abe</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer IV – Claims</t>
+          <t>DevOps Engineer, Level 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>FJA-US Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, MLflow, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91758534ce0e5b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist - environmental engineering</t>
+          <t>Imaging Data Scientist, Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, CI/CD, GitHub Actions, Git, Databricks</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, OpenCV, YOLO, Docker, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578709967a95284d</t>
+          <t>https://www.indeed.com/viewjob?jk=5690120fbfb8676d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distinguished AI and Data Security Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, BigQuery, PostgreSQL, MongoDB, Python</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d3211f519b547f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e00e9079f14e290</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Backend Engineer, Machine Learning Data Pipelines</t>
+          <t>Java Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, Kafka, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb735b6e832f4be</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4705ad07596c72</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Ads Quality</t>
+          <t>Java Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, XGBoost, Git, Kafka, Python, SQL</t>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acca62b3803b106e</t>
+          <t>https://www.indeed.com/viewjob?jk=47fb7b310145254c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack / Platform Engineer (Python, React, AWS)</t>
+          <t>Java Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ACA Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee7562b01a357bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6208378c5e3463</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist - Data Sciences</t>
+          <t>Java Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Jenkins, Git, Python</t>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e50d19e7c72a84a</t>
+          <t>https://www.indeed.com/viewjob?jk=48c6e1162ba69d50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Agentic AI, Java/Python</t>
+          <t>Software Engineer (MTS), Frontier Strike (EntSecTech)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f13d9775a0da739</t>
+          <t>https://www.indeed.com/viewjob?jk=c53952fe2895f873</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Associate, Data Scientist - Applied AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Kafka, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d06d511ed0f968</t>
+          <t>https://www.indeed.com/viewjob?jk=becfb18a1f456e8b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>Data Lake, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56cfd8740b4c9353</t>
+          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Founding Platform Engineer -- Ruby on Rails</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frost</t>
+          <t>EASYLLAMA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Snowflake, Databricks, Kafka, Hadoop, MongoDB, Cassandra, Python, SQL</t>
+          <t>RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a8e010316c8d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=a98a7991b8fc19cd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Bronco Wine Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Ceres, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Power BI, Python, SQL</t>
+          <t>RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64273acc6be18246</t>
+          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ae0bf58018f888</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Business System Support Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Healthcare Finance Direct LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, Copilot, PostgreSQL, MySQL, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dce389fccfb3534</t>
+          <t>https://www.indeed.com/viewjob?jk=2a1d30c91f8aa4f9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Research Software Engineer I - Laboratory of Dr. Talmo Pereira</t>
+          <t>AI Solutions Engineer (NPI Function)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Salk Institute for Biological Studies</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c8a09a4a3e3a93</t>
+          <t>https://www.indeed.com/viewjob?jk=cae76d45fb41d88d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Copilot, Athena, Docker, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Snowflake, Kafka, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00f231ced225306d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbe72b0a6fd7b24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer, AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Java</t>
+          <t>RAG, Data Lake, Git, Databricks, PySpark, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ca885ed0f9397f</t>
+          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer IV NA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Java</t>
+          <t>Generative AI, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1cb78c97513d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd555ed93417011b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data and Platform Engineer</t>
+          <t>Senior Applications &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>The Community Foundation for Greater Atlanta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Synapse, AKS, Tableau, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,707 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr Advanced R&amp;D Engr/Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Solstice Advanced Materials</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Morris Plains, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, NoSQL, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb1d1cfc1c07833</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Big Data Architect</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38ecde40997dfe59</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa8366af2ac5a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Engineering Associate</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ecb961e115a14</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Translational Genomics</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Broad Institute</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbeeffeef0673e92</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd4f351d14491</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc24126bb01a3b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Scientist - Financial Crimes</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>TikTok USDS JV</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Matplotlib, Python, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00e1306f1d8a60d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>City of Chattanooga, TN</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Chattanooga, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed060f50574399f</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Associate Actuary II</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Wildfire Defense Systems</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfc7194d4a210ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Solutions Engineer (Presales)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ARANGO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8bc8a97be7122f</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern (PhD) - Summer 2027</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ab56412a7aa66a</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern (Masters) - Summer 2027</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54148c4e2dbea934</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior AWS DevOps Architect</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>KNS IT Group</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55665d3cb959d92b</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Intern, AI Software Engineering (June-August 2027)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Rockwell Automation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Mayfield Heights, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cabbf109acd5ad78</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Co-op, AI Software Engineering (6-8 months)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Rockwell Automation</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Mayfield Heights, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4726a1256415836</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Non-Functional Junior Test Engineer - Officer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Citi</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0264c92af2393b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sr. Associate Data Engineer, AI Data Products</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Lincoln Financial</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Radnor, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Athena, FastAPI, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>External Post</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Menlo Security</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=962a74b9095da3ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst (Gas Engineering)</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>National Grid</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a54d2ee50c8485d9</t>
+          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-26.xlsx
+++ b/daily_matches/job_matches_2026-09-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Python Engineer</t>
+          <t>Software Engineer lll - Senior Databricks/Spark/AWS Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Generative AI, RAG, Copilot, S3, Glue, Athena, CI/CD, Jenkins, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dac7d146ce85fb43</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a9159a42796f24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, spaCy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef89900c1dc8244</t>
+          <t>https://www.indeed.com/viewjob?jk=5d53c57d3385a022</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic Data Engineer, IC2</t>
+          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, Glue, Kinesis, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a242ddcff013ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c536a9bd99ef94e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer, Customer Store Experience</t>
+          <t>Full-stack Engineer 4 (Apache Spark and Java)( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+          <t>RAG, Copilot, S3, Glue, Kinesis, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab9f52b7b9fec24</t>
+          <t>https://www.indeed.com/viewjob?jk=61acd17e8e4caf4c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa6bfaadd5a59007</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7a1bd8af02f9dc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f995067a8af808</t>
+          <t>https://www.indeed.com/viewjob?jk=a07d991630064dac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,137 +706,137 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4efa0feb82038a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1b607fdff26a44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Level 3</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FJA-US Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a87d8ccc941480</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46e42976391c6a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Imaging Data Scientist, Machine Learning Engineer, Computer Vision</t>
+          <t>Full-stack Engineer 5 (Java, Spring Boot, AWS, CI/CD) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, OpenCV, YOLO, Docker, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5690120fbfb8676d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e33ea940cfabaf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e00e9079f14e290</t>
+          <t>https://www.indeed.com/viewjob?jk=c52f54f8e5be210c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-Software Engineer III</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4705ad07596c72</t>
+          <t>https://www.indeed.com/viewjob?jk=bca244a4074f26cb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-Software Engineer III</t>
+          <t>Full Stack Engineer - 4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fb7b310145254c</t>
+          <t>https://www.indeed.com/viewjob?jk=4acbff2d0e6ba792</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-Software Engineer III</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6208378c5e3463</t>
+          <t>https://www.indeed.com/viewjob?jk=a726f18ef6bec68d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-Software Engineer III</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c6e1162ba69d50</t>
+          <t>https://www.indeed.com/viewjob?jk=9360083577d366e1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer (MTS), Frontier Strike (EntSecTech)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53952fe2895f873</t>
+          <t>https://www.indeed.com/viewjob?jk=26af012597a937ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - Applied AI</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, API, UI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becfb18a1f456e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a471487d6e7ce5e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c121478651fef59</t>
+          <t>https://www.indeed.com/viewjob?jk=206971bfe0c7648e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Founding Platform Engineer -- Ruby on Rails</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EASYLLAMA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a98a7991b8fc19cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f700dc035e701b44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bronco Wine Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ceres, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e558da34cfe637e</t>
+          <t>https://www.indeed.com/viewjob?jk=cbde946ea5f19114</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
+          <t>Full-stack Engineer 4 (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ab6a43be12efda</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21d9e3e95a919b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business System Support Analyst</t>
+          <t>Full-stack Engineer 4 (Cloud Native, Microservices &amp; AWS) ( Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Healthcare Finance Direct LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, PostgreSQL, MySQL, Tableau, Power BI, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a1d30c91f8aa4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=befbf1e1c644225d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer (NPI Function)</t>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Git, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,147 +1231,252 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae76d45fb41d88d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc7880b49c1e317</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, TRM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Kafka, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbe72b0a6fd7b24</t>
+          <t>https://www.indeed.com/viewjob?jk=7d827e41dc43be7d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, AI</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, PySpark, Python, SQL, R, Java</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05fc81fdc3c7e4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ca86abf14784b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer IV NA</t>
+          <t>Full Stack Software Engineer, Integrity</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Docker, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd555ed93417011b</t>
+          <t>https://www.indeed.com/viewjob?jk=836233526c2bfe4c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Applications &amp; Data Analyst</t>
+          <t>Senior Associate, Data Scientist - Applied AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Community Foundation for Greater Atlanta</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3201b9df96bac4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, Integrity</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>National Basketball Association</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, AKS, Tableau, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67c100e86a4b30b0</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, MLflow, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=986e0cd967904817</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4, Enterprise CI/CD (AWS, Python, Groovy)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c866253f682ee0b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr AI Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Kubernetes, Terraform, Kafka, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d39e629d619ef892</t>
         </is>
       </c>
     </row>
